--- a/artfynd/A 40945-2020 artfynd.xlsx
+++ b/artfynd/A 40945-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40945-2020 artfynd.xlsx
+++ b/artfynd/A 40945-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1776,6 +1776,130 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114956467</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Cykelbanan öst Mjölnartorpet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>420420</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6585852</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Köpman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Köpman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40945-2020 artfynd.xlsx
+++ b/artfynd/A 40945-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>88795749</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420545.7137608728</v>
+        <v>420546</v>
       </c>
       <c r="R2" t="n">
-        <v>6586303.733175874</v>
+        <v>6586304</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,19 +757,9 @@
           <t>2020-10-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1046,7 +1036,7 @@
         <v>98466054</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>420464.6296587522</v>
+        <v>420464</v>
       </c>
       <c r="R5" t="n">
-        <v>6586377.752213774</v>
+        <v>6586378</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1120,19 +1110,9 @@
           <t>2021-10-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
